--- a/output/graficos_regionales_piramide/plot_regional_piramide_2023_los_rios.xlsx
+++ b/output/graficos_regionales_piramide/plot_regional_piramide_2023_los_rios.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">sexo</t>
   </si>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:17</t>
+    <t xml:space="preserve">2026-08-28 11:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -108,16 +108,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_piramide_2023_los_rios.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Piramide de poblacion</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Los Ríos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
 </sst>
 </file>
@@ -1031,23 +1040,23 @@
         <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_piramide/plot_regional_piramide_2023_los_rios.xlsx
+++ b/output/graficos_regionales_piramide/plot_regional_piramide_2023_los_rios.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:15</t>
+    <t xml:space="preserve">2026-09-06 17:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
